--- a/data/00_grape_db_versions_readme.xlsx
+++ b/data/00_grape_db_versions_readme.xlsx
@@ -120,7 +120,7 @@
     <t>DG25-11237</t>
   </si>
   <si>
-    <t>Komlan (INREA)</t>
+    <t>Komlan (INRAe)</t>
   </si>
   <si>
     <t>All markers</t>
